--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/187.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/187.xlsx
@@ -426,13 +426,13 @@
         <v>2.513941774870887</v>
       </c>
       <c r="E2">
-        <v>-16.49357840812652</v>
+        <v>-16.10265788941438</v>
       </c>
       <c r="F2">
-        <v>-1.074436572150815</v>
+        <v>-1.372268616520752</v>
       </c>
       <c r="G2">
-        <v>-8.720031069837269</v>
+        <v>-9.583060497015413</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>2.532176544814495</v>
       </c>
       <c r="E3">
-        <v>-15.80519601727254</v>
+        <v>-17.02979501537477</v>
       </c>
       <c r="F3">
-        <v>-1.223387799950402</v>
+        <v>-1.539425703099067</v>
       </c>
       <c r="G3">
-        <v>-8.367186505170666</v>
+        <v>-9.299909537041549</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>2.577780601299905</v>
       </c>
       <c r="E4">
-        <v>-16.08747391606666</v>
+        <v>-16.86623559116573</v>
       </c>
       <c r="F4">
-        <v>-0.6851337140615481</v>
+        <v>-1.237436911101882</v>
       </c>
       <c r="G4">
-        <v>-7.791082059881156</v>
+        <v>-9.015818382134531</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.654951082880967</v>
       </c>
       <c r="E5">
-        <v>-16.42136283312621</v>
+        <v>-16.84089425061881</v>
       </c>
       <c r="F5">
-        <v>-0.8014232435361538</v>
+        <v>-0.8140856676553471</v>
       </c>
       <c r="G5">
-        <v>-7.747343132216305</v>
+        <v>-8.98339489912291</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.772181859980484</v>
       </c>
       <c r="E6">
-        <v>-16.28012425730098</v>
+        <v>-18.25930740777533</v>
       </c>
       <c r="F6">
-        <v>-1.405455499779108</v>
+        <v>-1.241296274831525</v>
       </c>
       <c r="G6">
-        <v>-6.795452041673043</v>
+        <v>-8.627603948926357</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.934909144314452</v>
       </c>
       <c r="E7">
-        <v>-17.0227849376109</v>
+        <v>-18.49714286265817</v>
       </c>
       <c r="F7">
-        <v>-0.5597048070318553</v>
+        <v>-1.080553237053086</v>
       </c>
       <c r="G7">
-        <v>-7.776138257316886</v>
+        <v>-8.622561988070046</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.141734125536563</v>
       </c>
       <c r="E8">
-        <v>-17.79032052564495</v>
+        <v>-19.48503852437948</v>
       </c>
       <c r="F8">
-        <v>-1.462395818312741</v>
+        <v>-1.073135206961017</v>
       </c>
       <c r="G8">
-        <v>-6.62562436605397</v>
+        <v>-7.917541588935777</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.394498636536762</v>
       </c>
       <c r="E9">
-        <v>-18.91235411594746</v>
+        <v>-18.7210351460714</v>
       </c>
       <c r="F9">
-        <v>-0.977425637241562</v>
+        <v>-0.8808032066442221</v>
       </c>
       <c r="G9">
-        <v>-5.915992376983495</v>
+        <v>-7.664245128635059</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.691901060552892</v>
       </c>
       <c r="E10">
-        <v>-20.73589361477818</v>
+        <v>-19.77648658303913</v>
       </c>
       <c r="F10">
-        <v>-0.8456588912130503</v>
+        <v>-1.150794650973471</v>
       </c>
       <c r="G10">
-        <v>-6.08594585333306</v>
+        <v>-7.203029855740415</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.024421909102353</v>
       </c>
       <c r="E11">
-        <v>-19.61527290836607</v>
+        <v>-20.65655927863781</v>
       </c>
       <c r="F11">
-        <v>-0.6694659730049982</v>
+        <v>-0.5800312863617496</v>
       </c>
       <c r="G11">
-        <v>-5.662957449780381</v>
+        <v>-7.269810180358593</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.374850281133041</v>
       </c>
       <c r="E12">
-        <v>-18.95613087417961</v>
+        <v>-20.38564332112893</v>
       </c>
       <c r="F12">
-        <v>-1.100122588576822</v>
+        <v>-1.118142893057323</v>
       </c>
       <c r="G12">
-        <v>-6.308176154293256</v>
+        <v>-6.970497137062007</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.725690466669683</v>
       </c>
       <c r="E13">
-        <v>-20.08094494752283</v>
+        <v>-22.42418118042182</v>
       </c>
       <c r="F13">
-        <v>-0.8413944558234384</v>
+        <v>-0.6395412005788661</v>
       </c>
       <c r="G13">
-        <v>-5.203334549290126</v>
+        <v>-6.631603211297894</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.058727721628271</v>
       </c>
       <c r="E14">
-        <v>-21.18957878323664</v>
+        <v>-21.7521918654756</v>
       </c>
       <c r="F14">
-        <v>-0.2203094282264531</v>
+        <v>-0.4038723312172123</v>
       </c>
       <c r="G14">
-        <v>-4.756745266587982</v>
+        <v>-5.52273598291901</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>5.351894102578549</v>
       </c>
       <c r="E15">
-        <v>-21.59897094742607</v>
+        <v>-22.64833611532749</v>
       </c>
       <c r="F15">
-        <v>0.3383481751607559</v>
+        <v>-0.2850016089154833</v>
       </c>
       <c r="G15">
-        <v>-5.505660189027449</v>
+        <v>-5.798110471421126</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.586550879403286</v>
       </c>
       <c r="E16">
-        <v>-22.5006852203074</v>
+        <v>-23.10658145711167</v>
       </c>
       <c r="F16">
-        <v>0.2710830853186305</v>
+        <v>0.128523540399044</v>
       </c>
       <c r="G16">
-        <v>-3.971053493752751</v>
+        <v>-5.402142740559978</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.750382530883212</v>
       </c>
       <c r="E17">
-        <v>-22.84949545922222</v>
+        <v>-24.00075582077023</v>
       </c>
       <c r="F17">
-        <v>0.9348911617150003</v>
+        <v>0.4507220119223285</v>
       </c>
       <c r="G17">
-        <v>-3.302929124653658</v>
+        <v>-5.425674098253118</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.835508280244463</v>
       </c>
       <c r="E18">
-        <v>-25.03548043220485</v>
+        <v>-24.44201938502564</v>
       </c>
       <c r="F18">
-        <v>1.057509418146994</v>
+        <v>0.3683359035095008</v>
       </c>
       <c r="G18">
-        <v>-4.514486165115195</v>
+        <v>-5.78914551410078</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.834478435785365</v>
       </c>
       <c r="E19">
-        <v>-26.24850465074348</v>
+        <v>-25.26136524418146</v>
       </c>
       <c r="F19">
-        <v>1.239740306354052</v>
+        <v>0.803961066763316</v>
       </c>
       <c r="G19">
-        <v>-4.107553907427981</v>
+        <v>-6.081148872846656</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.744256580847058</v>
       </c>
       <c r="E20">
-        <v>-25.65426470603495</v>
+        <v>-25.92246810761324</v>
       </c>
       <c r="F20">
-        <v>1.134101924944642</v>
+        <v>1.124290741425885</v>
       </c>
       <c r="G20">
-        <v>-3.18495452381619</v>
+        <v>-5.891775736363726</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.566755321856192</v>
       </c>
       <c r="E21">
-        <v>-26.70457632500398</v>
+        <v>-26.25650193584103</v>
       </c>
       <c r="F21">
-        <v>1.132360696663958</v>
+        <v>1.254871265333588</v>
       </c>
       <c r="G21">
-        <v>-4.713337393477058</v>
+        <v>-5.495460398220954</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.306924346315089</v>
       </c>
       <c r="E22">
-        <v>-25.25891986821732</v>
+        <v>-27.04739539280665</v>
       </c>
       <c r="F22">
-        <v>1.458182447207087</v>
+        <v>1.34412950972004</v>
       </c>
       <c r="G22">
-        <v>-2.919137580285949</v>
+        <v>-5.417285175856605</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.971093134034473</v>
       </c>
       <c r="E23">
-        <v>-26.96062983081968</v>
+        <v>-27.10253409232404</v>
       </c>
       <c r="F23">
-        <v>1.758319838059015</v>
+        <v>1.686488787092659</v>
       </c>
       <c r="G23">
-        <v>-3.22315490879384</v>
+        <v>-5.735620613821844</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.567351516704614</v>
       </c>
       <c r="E24">
-        <v>-26.48867679821429</v>
+        <v>-27.32327455782793</v>
       </c>
       <c r="F24">
-        <v>1.26794455968457</v>
+        <v>1.512402407189926</v>
       </c>
       <c r="G24">
-        <v>-3.569951106760193</v>
+        <v>-4.524805135561103</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.110453940079238</v>
       </c>
       <c r="E25">
-        <v>-27.81421095347348</v>
+        <v>-27.34460819887807</v>
       </c>
       <c r="F25">
-        <v>1.695857622418321</v>
+        <v>1.855732531158626</v>
       </c>
       <c r="G25">
-        <v>-3.99631626676293</v>
+        <v>-4.950117542082351</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.614147624797435</v>
       </c>
       <c r="E26">
-        <v>-27.54948089145908</v>
+        <v>-27.59263272027817</v>
       </c>
       <c r="F26">
-        <v>1.570154525778302</v>
+        <v>1.653652303245686</v>
       </c>
       <c r="G26">
-        <v>-3.704948532760594</v>
+        <v>-5.521544186524872</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.092265658342901</v>
       </c>
       <c r="E27">
-        <v>-27.80639027886224</v>
+        <v>-28.53058837064289</v>
       </c>
       <c r="F27">
-        <v>1.912671192957453</v>
+        <v>1.706106183925757</v>
       </c>
       <c r="G27">
-        <v>-3.578406240067492</v>
+        <v>-5.547859713016539</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.556064958180789</v>
       </c>
       <c r="E28">
-        <v>-26.95033660940025</v>
+        <v>-27.73820051725474</v>
       </c>
       <c r="F28">
-        <v>2.274127652434212</v>
+        <v>1.694142901894526</v>
       </c>
       <c r="G28">
-        <v>-4.318352894641073</v>
+        <v>-6.226140835830116</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.023510585328091</v>
       </c>
       <c r="E29">
-        <v>-26.18824424712341</v>
+        <v>-27.18827169071126</v>
       </c>
       <c r="F29">
-        <v>1.592048276234293</v>
+        <v>1.960252616574256</v>
       </c>
       <c r="G29">
-        <v>-4.059064346914275</v>
+        <v>-6.023581796464269</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.507726691395007</v>
       </c>
       <c r="E30">
-        <v>-27.7194028216489</v>
+        <v>-26.92756744208968</v>
       </c>
       <c r="F30">
-        <v>2.008115685108012</v>
+        <v>1.943546102794596</v>
       </c>
       <c r="G30">
-        <v>-3.809111537608223</v>
+        <v>-5.601679251848471</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.018840304556386</v>
       </c>
       <c r="E31">
-        <v>-26.7643385964832</v>
+        <v>-27.67480640962136</v>
       </c>
       <c r="F31">
-        <v>1.611728628990003</v>
+        <v>1.794323998854293</v>
       </c>
       <c r="G31">
-        <v>-4.366114135136139</v>
+        <v>-6.226114351465802</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.5661620581975338</v>
       </c>
       <c r="E32">
-        <v>-27.10048722207257</v>
+        <v>-27.09357224226286</v>
       </c>
       <c r="F32">
-        <v>1.810004993789288</v>
+        <v>1.940355231559012</v>
       </c>
       <c r="G32">
-        <v>-4.333958806313198</v>
+        <v>-6.643123909774558</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1595073568321572</v>
       </c>
       <c r="E33">
-        <v>-26.62516953327948</v>
+        <v>-27.03363788877134</v>
       </c>
       <c r="F33">
-        <v>1.519682099925728</v>
+        <v>1.659860088562266</v>
       </c>
       <c r="G33">
-        <v>-4.966229967221985</v>
+        <v>-6.151776051381468</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1965911913526648</v>
       </c>
       <c r="E34">
-        <v>-26.26347578581284</v>
+        <v>-26.9237408815532</v>
       </c>
       <c r="F34">
-        <v>1.211090391360828</v>
+        <v>1.424653448211374</v>
       </c>
       <c r="G34">
-        <v>-3.944936599993441</v>
+        <v>-6.12060395458369</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.5025837075636308</v>
       </c>
       <c r="E35">
-        <v>-26.31514567424036</v>
+        <v>-26.37299692968834</v>
       </c>
       <c r="F35">
-        <v>1.518842135379289</v>
+        <v>1.666183845315237</v>
       </c>
       <c r="G35">
-        <v>-4.657167367312244</v>
+        <v>-6.97780020052164</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.758006071178346</v>
       </c>
       <c r="E36">
-        <v>-23.26347496758142</v>
+        <v>-26.03788985312074</v>
       </c>
       <c r="F36">
-        <v>1.640413335414145</v>
+        <v>1.360285987544242</v>
       </c>
       <c r="G36">
-        <v>-4.553898209760218</v>
+        <v>-6.736769311443922</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.9640958418396863</v>
       </c>
       <c r="E37">
-        <v>-25.75304883803827</v>
+        <v>-26.12609094136813</v>
       </c>
       <c r="F37">
-        <v>1.058220157378596</v>
+        <v>1.314016697893472</v>
       </c>
       <c r="G37">
-        <v>-5.05218828214916</v>
+        <v>-5.845683010820453</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.12435603537922</v>
       </c>
       <c r="E38">
-        <v>-23.04042950880762</v>
+        <v>-24.97528342722089</v>
       </c>
       <c r="F38">
-        <v>2.270598807298286</v>
+        <v>1.479319069856919</v>
       </c>
       <c r="G38">
-        <v>-4.615159854964432</v>
+        <v>-6.441442164976618</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.244881135030521</v>
       </c>
       <c r="E39">
-        <v>-23.8561525887573</v>
+        <v>-25.21968064094085</v>
       </c>
       <c r="F39">
-        <v>1.658632448071317</v>
+        <v>1.653711945698688</v>
       </c>
       <c r="G39">
-        <v>-4.859951523774761</v>
+        <v>-5.269078673154512</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.329098729722841</v>
       </c>
       <c r="E40">
-        <v>-23.31290326137514</v>
+        <v>-24.18607909106013</v>
       </c>
       <c r="F40">
-        <v>1.630502747807052</v>
+        <v>1.369707838383683</v>
       </c>
       <c r="G40">
-        <v>-4.975396867820226</v>
+        <v>-6.308186085929874</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.381393724410087</v>
       </c>
       <c r="E41">
-        <v>-23.33489805963039</v>
+        <v>-24.93684573984378</v>
       </c>
       <c r="F41">
-        <v>1.838244038550723</v>
+        <v>1.386734101980824</v>
       </c>
       <c r="G41">
-        <v>-4.363151196878492</v>
+        <v>-5.943691711510577</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.405995646600505</v>
       </c>
       <c r="E42">
-        <v>-24.08564206604401</v>
+        <v>-24.1232465142037</v>
       </c>
       <c r="F42">
-        <v>1.294738931695522</v>
+        <v>1.091245508993407</v>
       </c>
       <c r="G42">
-        <v>-4.120345855391725</v>
+        <v>-6.581958270390984</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.406809056594571</v>
       </c>
       <c r="E43">
-        <v>-23.01770562623713</v>
+        <v>-24.50177259955685</v>
       </c>
       <c r="F43">
-        <v>1.932921462486289</v>
+        <v>1.264500208023729</v>
       </c>
       <c r="G43">
-        <v>-4.277629873962499</v>
+        <v>-6.158959935201686</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.386251116738989</v>
       </c>
       <c r="E44">
-        <v>-21.78880910630162</v>
+        <v>-22.14971037081692</v>
       </c>
       <c r="F44">
-        <v>1.55847785886844</v>
+        <v>1.198484296225025</v>
       </c>
       <c r="G44">
-        <v>-6.409942324170452</v>
+        <v>-6.732677477157383</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.346715782606322</v>
       </c>
       <c r="E45">
-        <v>-22.53155129914368</v>
+        <v>-22.34097047053087</v>
       </c>
       <c r="F45">
-        <v>1.570699591529344</v>
+        <v>1.240909961126805</v>
       </c>
       <c r="G45">
-        <v>-4.593952500239861</v>
+        <v>-5.456061595758088</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.290443376572482</v>
       </c>
       <c r="E46">
-        <v>-22.43710544523971</v>
+        <v>-22.05986997497874</v>
       </c>
       <c r="F46">
-        <v>1.531188123150613</v>
+        <v>1.103791961676208</v>
       </c>
       <c r="G46">
-        <v>-5.143479885940103</v>
+        <v>-5.850824288042942</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.220134159317954</v>
       </c>
       <c r="E47">
-        <v>-21.17386950690403</v>
+        <v>-22.15039417039207</v>
       </c>
       <c r="F47">
-        <v>1.787973734344432</v>
+        <v>1.172135585876779</v>
       </c>
       <c r="G47">
-        <v>-5.229511032869143</v>
+        <v>-6.491156627339853</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.13889527405492</v>
       </c>
       <c r="E48">
-        <v>-20.44541012108216</v>
+        <v>-21.86130544669041</v>
       </c>
       <c r="F48">
-        <v>1.695088897468523</v>
+        <v>1.14582166695945</v>
       </c>
       <c r="G48">
-        <v>-4.272544876014178</v>
+        <v>-6.432225606195287</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.049211185126877</v>
       </c>
       <c r="E49">
-        <v>-20.14611874544122</v>
+        <v>-21.66365114167763</v>
       </c>
       <c r="F49">
-        <v>1.451426282669855</v>
+        <v>1.100221698170142</v>
       </c>
       <c r="G49">
-        <v>-5.161969282776933</v>
+        <v>-6.00091118061134</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9528173736159686</v>
       </c>
       <c r="E50">
-        <v>-19.68444082035923</v>
+        <v>-20.67961373981086</v>
       </c>
       <c r="F50">
-        <v>0.8564331715262479</v>
+        <v>1.145662620418112</v>
       </c>
       <c r="G50">
-        <v>-4.666493174096371</v>
+        <v>-6.175582184354367</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8516648354098842</v>
       </c>
       <c r="E51">
-        <v>-18.80218087181485</v>
+        <v>-19.47854469265248</v>
       </c>
       <c r="F51">
-        <v>1.518601908832478</v>
+        <v>0.9030669428342489</v>
       </c>
       <c r="G51">
-        <v>-4.838555467954452</v>
+        <v>-5.412825871015206</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.7472336655881653</v>
       </c>
       <c r="E52">
-        <v>-19.49318072064527</v>
+        <v>-20.13462094993574</v>
       </c>
       <c r="F52">
-        <v>1.304732356042896</v>
+        <v>0.8900483207318518</v>
       </c>
       <c r="G52">
-        <v>-5.549425601056615</v>
+        <v>-5.896470089938413</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6405963417733603</v>
       </c>
       <c r="E53">
-        <v>-18.82394924636972</v>
+        <v>-19.64141126033834</v>
       </c>
       <c r="F53">
-        <v>1.571793036501039</v>
+        <v>0.9294421609393851</v>
       </c>
       <c r="G53">
-        <v>-5.06172927439334</v>
+        <v>-6.708973971096201</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.5318497894198058</v>
       </c>
       <c r="E54">
-        <v>-19.01680789740839</v>
+        <v>-19.54935191223641</v>
       </c>
       <c r="F54">
-        <v>1.72593232934436</v>
+        <v>1.030893973495046</v>
       </c>
       <c r="G54">
-        <v>-5.976327069436713</v>
+        <v>-7.349107677660756</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.4227193639881706</v>
       </c>
       <c r="E55">
-        <v>-19.15116319274196</v>
+        <v>-18.93485610329158</v>
       </c>
       <c r="F55">
-        <v>1.579629392131523</v>
+        <v>0.9151776742631776</v>
       </c>
       <c r="G55">
-        <v>-6.594938919450466</v>
+        <v>-6.832556636077195</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.3140633291890657</v>
       </c>
       <c r="E56">
-        <v>-18.17153199608465</v>
+        <v>-18.96084048714759</v>
       </c>
       <c r="F56">
-        <v>1.511289081400564</v>
+        <v>1.005038970118868</v>
       </c>
       <c r="G56">
-        <v>-5.710818006641624</v>
+        <v>-6.60118591888307</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.2065656633383184</v>
       </c>
       <c r="E57">
-        <v>-18.33186714680023</v>
+        <v>-17.91034320074425</v>
       </c>
       <c r="F57">
-        <v>1.222031468017004</v>
+        <v>1.139449864897116</v>
       </c>
       <c r="G57">
-        <v>-5.628978010365301</v>
+        <v>-6.571440667212719</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.09994448020674342</v>
       </c>
       <c r="E58">
-        <v>-17.40367941487006</v>
+        <v>-17.52916795809661</v>
       </c>
       <c r="F58">
-        <v>2.101341809353874</v>
+        <v>1.022739524781888</v>
       </c>
       <c r="G58">
-        <v>-6.145310555943271</v>
+        <v>-7.030292210592323</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.004869641868293185</v>
       </c>
       <c r="E59">
-        <v>-15.62553333949222</v>
+        <v>-18.83650670479299</v>
       </c>
       <c r="F59">
-        <v>1.048862919196573</v>
+        <v>0.7629171186894061</v>
       </c>
       <c r="G59">
-        <v>-6.919167128475607</v>
+        <v>-6.789887014621528</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.1072751535592139</v>
       </c>
       <c r="E60">
-        <v>-16.57144551868842</v>
+        <v>-17.33564362137882</v>
       </c>
       <c r="F60">
-        <v>1.525190743154345</v>
+        <v>0.7507881631776158</v>
       </c>
       <c r="G60">
-        <v>-6.738037250385463</v>
+        <v>-6.741903967575332</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.207216163846604</v>
       </c>
       <c r="E61">
-        <v>-16.24649580932001</v>
+        <v>-17.59449572413126</v>
       </c>
       <c r="F61">
-        <v>1.334575120096151</v>
+        <v>0.8041930096360999</v>
       </c>
       <c r="G61">
-        <v>-7.287683815725119</v>
+        <v>-6.367660036542881</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.3047562940377161</v>
       </c>
       <c r="E62">
-        <v>-15.19223988949031</v>
+        <v>-17.49383680388877</v>
       </c>
       <c r="F62">
-        <v>1.009502213685152</v>
+        <v>0.456152788615082</v>
       </c>
       <c r="G62">
-        <v>-7.064066396183968</v>
+        <v>-7.045646520803463</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.399528900158344</v>
       </c>
       <c r="E63">
-        <v>-16.94932856073248</v>
+        <v>-17.2977901071487</v>
       </c>
       <c r="F63">
-        <v>0.8947103724748074</v>
+        <v>0.7490900100018768</v>
       </c>
       <c r="G63">
-        <v>-6.774128817854598</v>
+        <v>-6.936451486736142</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.4906651279806624</v>
       </c>
       <c r="E64">
-        <v>-15.35874282180433</v>
+        <v>-16.82511704717609</v>
       </c>
       <c r="F64">
-        <v>0.652140374280431</v>
+        <v>0.7729585883461417</v>
       </c>
       <c r="G64">
-        <v>-6.858584145106945</v>
+        <v>-7.157887256766913</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.5787439092719393</v>
       </c>
       <c r="E65">
-        <v>-16.39491654492141</v>
+        <v>-17.72052768423874</v>
       </c>
       <c r="F65">
-        <v>1.161018895331209</v>
+        <v>0.4928652035397533</v>
       </c>
       <c r="G65">
-        <v>-6.607813631052691</v>
+        <v>-7.029500990208438</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.6640117466953515</v>
       </c>
       <c r="E66">
-        <v>-15.61658507485307</v>
+        <v>-16.28553125526613</v>
       </c>
       <c r="F66">
-        <v>1.192245032947139</v>
+        <v>0.7550443148931997</v>
       </c>
       <c r="G66">
-        <v>-5.913860385656204</v>
+        <v>-6.637939595460059</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.7466194684341584</v>
       </c>
       <c r="E67">
-        <v>-15.55740244804682</v>
+        <v>-16.86104143147893</v>
       </c>
       <c r="F67">
-        <v>0.9738476239338555</v>
+        <v>0.7917393341024122</v>
       </c>
       <c r="G67">
-        <v>-7.069128220313513</v>
+        <v>-7.262146267435181</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.8263209668124237</v>
       </c>
       <c r="E68">
-        <v>-15.11121643254507</v>
+        <v>-16.58243612510503</v>
       </c>
       <c r="F68">
-        <v>0.9275700506090583</v>
+        <v>0.7947810992054919</v>
       </c>
       <c r="G68">
-        <v>-6.849645672150912</v>
+        <v>-7.500886258999723</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.905100158934219</v>
       </c>
       <c r="E69">
-        <v>-14.81929741258862</v>
+        <v>-17.08511485385247</v>
       </c>
       <c r="F69">
-        <v>1.079452870647153</v>
+        <v>0.4051750586468004</v>
       </c>
       <c r="G69">
-        <v>-6.612776138816058</v>
+        <v>-7.536941410467925</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.985165530409198</v>
       </c>
       <c r="E70">
-        <v>-14.81921137158247</v>
+        <v>-16.66283465263721</v>
       </c>
       <c r="F70">
-        <v>1.570408006203559</v>
+        <v>0.6617858843186285</v>
       </c>
       <c r="G70">
-        <v>-7.408469069725428</v>
+        <v>-7.339963950881289</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.068405458832191</v>
       </c>
       <c r="E71">
-        <v>-16.36414556403929</v>
+        <v>-16.58174779705586</v>
       </c>
       <c r="F71">
-        <v>1.580141323186453</v>
+        <v>0.2411318051356087</v>
       </c>
       <c r="G71">
-        <v>-6.69426190671968</v>
+        <v>-7.460682993970813</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.156632874511549</v>
       </c>
       <c r="E72">
-        <v>-14.04916248047416</v>
+        <v>-17.47045629258717</v>
       </c>
       <c r="F72">
-        <v>0.8908899420130961</v>
+        <v>0.7978775365571564</v>
       </c>
       <c r="G72">
-        <v>-6.204354135636173</v>
+        <v>-7.919782828265863</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.253273102147324</v>
       </c>
       <c r="E73">
-        <v>-16.30161639494138</v>
+        <v>-17.19637493174692</v>
       </c>
       <c r="F73">
-        <v>1.163212412213822</v>
+        <v>0.3667512366679453</v>
       </c>
       <c r="G73">
-        <v>-5.923540420813033</v>
+        <v>-6.701975477826181</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.361203569371302</v>
       </c>
       <c r="E74">
-        <v>-16.35357610570539</v>
+        <v>-16.30808758429834</v>
       </c>
       <c r="F74">
-        <v>0.6785520405512905</v>
+        <v>0.542334476467537</v>
       </c>
       <c r="G74">
-        <v>-6.099370115494804</v>
+        <v>-6.136037717887772</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.480695053880235</v>
       </c>
       <c r="E75">
-        <v>-17.82617698283769</v>
+        <v>-17.40994682289667</v>
       </c>
       <c r="F75">
-        <v>1.036336347331439</v>
+        <v>0.3249485040530711</v>
       </c>
       <c r="G75">
-        <v>-7.403523114689757</v>
+        <v>-6.855012066470071</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.612464920441117</v>
       </c>
       <c r="E76">
-        <v>-16.69942019414518</v>
+        <v>-17.13198908830587</v>
       </c>
       <c r="F76">
-        <v>0.5181005880986375</v>
+        <v>0.3535520304717381</v>
       </c>
       <c r="G76">
-        <v>-6.182024505973788</v>
+        <v>-7.130707677889497</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.757681777684198</v>
       </c>
       <c r="E77">
-        <v>-16.43728947621118</v>
+        <v>-18.63198723318457</v>
       </c>
       <c r="F77">
-        <v>0.4085680515286672</v>
+        <v>-0.03496636368707769</v>
       </c>
       <c r="G77">
-        <v>-6.204940102196623</v>
+        <v>-6.201953990120201</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.916210405198327</v>
       </c>
       <c r="E78">
-        <v>-16.34769361796942</v>
+        <v>-17.82521694634806</v>
       </c>
       <c r="F78">
-        <v>0.1864769522663001</v>
+        <v>0.1818356097084145</v>
       </c>
       <c r="G78">
-        <v>-6.414775720657788</v>
+        <v>-6.647189259696783</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.083795040177715</v>
       </c>
       <c r="E79">
-        <v>-16.92069954805599</v>
+        <v>-18.31382570635367</v>
       </c>
       <c r="F79">
-        <v>0.7083575280714195</v>
+        <v>-0.002227627193635623</v>
       </c>
       <c r="G79">
-        <v>-5.954914460888706</v>
+        <v>-6.772404023628637</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.258933640582872</v>
       </c>
       <c r="E80">
-        <v>-16.98866741443711</v>
+        <v>-18.20591669922489</v>
       </c>
       <c r="F80">
-        <v>0.03899276313707058</v>
+        <v>-0.1065994348441649</v>
       </c>
       <c r="G80">
-        <v>-5.482751213895693</v>
+        <v>-6.314333768996301</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.439020893131737</v>
       </c>
       <c r="E81">
-        <v>-16.90747187547958</v>
+        <v>-19.40262482591389</v>
       </c>
       <c r="F81">
-        <v>0.3650928451275408</v>
+        <v>-0.060911659110161</v>
       </c>
       <c r="G81">
-        <v>-6.27154496790122</v>
+        <v>-5.956672360570059</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.61926205397871</v>
       </c>
       <c r="E82">
-        <v>-17.89729666712815</v>
+        <v>-20.17805807261732</v>
       </c>
       <c r="F82">
-        <v>0.4094759422021355</v>
+        <v>0.1693993298901856</v>
       </c>
       <c r="G82">
-        <v>-5.619754830492892</v>
+        <v>-6.400791976299907</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.792394163707465</v>
       </c>
       <c r="E83">
-        <v>-19.45073080529737</v>
+        <v>-21.36322311906076</v>
       </c>
       <c r="F83">
-        <v>-0.2314468279570924</v>
+        <v>-0.1097331487289555</v>
       </c>
       <c r="G83">
-        <v>-4.190522799733195</v>
+        <v>-5.717124595893935</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.95305303140674</v>
       </c>
       <c r="E84">
-        <v>-20.09729273869052</v>
+        <v>-21.01784093496975</v>
       </c>
       <c r="F84">
-        <v>0.290197663138229</v>
+        <v>-0.3113296100786599</v>
       </c>
       <c r="G84">
-        <v>-4.468582140667661</v>
+        <v>-7.008892844226474</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.096203117792561</v>
       </c>
       <c r="E85">
-        <v>-20.24520175672905</v>
+        <v>-22.51447442366075</v>
       </c>
       <c r="F85">
-        <v>0.3795047812014465</v>
+        <v>-0.1950732153001661</v>
       </c>
       <c r="G85">
-        <v>-5.154278885489205</v>
+        <v>-6.456399209723045</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.214805016948631</v>
       </c>
       <c r="E86">
-        <v>-20.92662388303324</v>
+        <v>-22.91527607265764</v>
       </c>
       <c r="F86">
-        <v>-0.2949370475446605</v>
+        <v>-0.3502496241317919</v>
       </c>
       <c r="G86">
-        <v>-6.076778952734818</v>
+        <v>-6.238439512508508</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.302184412345267</v>
       </c>
       <c r="E87">
-        <v>-24.2374229293591</v>
+        <v>-24.02623301553738</v>
       </c>
       <c r="F87">
-        <v>-0.2291895267844638</v>
+        <v>-0.4248606761019434</v>
       </c>
       <c r="G87">
-        <v>-4.946707680176902</v>
+        <v>-5.766802642256239</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.353686840386106</v>
       </c>
       <c r="E88">
-        <v>-22.90811655525151</v>
+        <v>-24.22279142984031</v>
       </c>
       <c r="F88">
-        <v>-0.480102013092434</v>
+        <v>-0.5997961325925458</v>
       </c>
       <c r="G88">
-        <v>-4.600305437129722</v>
+        <v>-6.108225824812355</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.36643731104046</v>
       </c>
       <c r="E89">
-        <v>-25.4703271487914</v>
+        <v>-25.99035898993623</v>
       </c>
       <c r="F89">
-        <v>-0.1726749890958703</v>
+        <v>-0.8820780640771305</v>
       </c>
       <c r="G89">
-        <v>-4.986348152464135</v>
+        <v>-6.218784803641856</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.336593417900685</v>
       </c>
       <c r="E90">
-        <v>-27.07885017326392</v>
+        <v>-27.00240953201445</v>
       </c>
       <c r="F90">
-        <v>-0.05480741971893145</v>
+        <v>-0.9017252821367292</v>
       </c>
       <c r="G90">
-        <v>-6.158744749741634</v>
+        <v>-6.632066687673392</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.262468170135894</v>
       </c>
       <c r="E91">
-        <v>-29.21116820078166</v>
+        <v>-28.74190508173682</v>
       </c>
       <c r="F91">
-        <v>-0.8770962625166943</v>
+        <v>-0.7711099667981087</v>
       </c>
       <c r="G91">
-        <v>-5.171122941193017</v>
+        <v>-6.236426700820632</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.145422565420066</v>
       </c>
       <c r="E92">
-        <v>-29.91989702535211</v>
+        <v>-30.91238003124318</v>
       </c>
       <c r="F92">
-        <v>-0.5824227830536317</v>
+        <v>-0.9802371162066635</v>
       </c>
       <c r="G92">
-        <v>-5.212561039708074</v>
+        <v>-6.486157703575554</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.989076243422731</v>
       </c>
       <c r="E93">
-        <v>-30.3259018909838</v>
+        <v>-31.59132281802818</v>
       </c>
       <c r="F93">
-        <v>-0.2007856369098715</v>
+        <v>-1.239236953468165</v>
       </c>
       <c r="G93">
-        <v>-5.940937337621904</v>
+        <v>-6.445732631995513</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.797074813271093</v>
       </c>
       <c r="E94">
-        <v>-33.11443655847903</v>
+        <v>-33.01252098669941</v>
       </c>
       <c r="F94">
-        <v>-1.093099689735888</v>
+        <v>-1.21317568660869</v>
       </c>
       <c r="G94">
-        <v>-6.533677274246252</v>
+        <v>-6.770252169028111</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.575799743101824</v>
       </c>
       <c r="E95">
-        <v>-35.32462169655867</v>
+        <v>-34.42204248514187</v>
       </c>
       <c r="F95">
-        <v>-0.8548206346880127</v>
+        <v>-1.351182524282491</v>
       </c>
       <c r="G95">
-        <v>-5.581395539329356</v>
+        <v>-6.848844520130409</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.334850149094712</v>
       </c>
       <c r="E96">
-        <v>-36.81138990462396</v>
+        <v>-37.2268660736427</v>
       </c>
       <c r="F96">
-        <v>-0.8034684826536658</v>
+        <v>-1.313962320139903</v>
       </c>
       <c r="G96">
-        <v>-5.035721628636826</v>
+        <v>-6.847199178997391</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.085822282632103</v>
       </c>
       <c r="E97">
-        <v>-37.15525731415941</v>
+        <v>-39.03070444630305</v>
       </c>
       <c r="F97">
-        <v>-1.819947353852703</v>
+        <v>-1.677725782833458</v>
       </c>
       <c r="G97">
-        <v>-6.200841646819006</v>
+        <v>-6.725142675510002</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.837087797709977</v>
       </c>
       <c r="E98">
-        <v>-40.19921602958328</v>
+        <v>-40.6107252553713</v>
       </c>
       <c r="F98">
-        <v>-1.135387845648802</v>
+        <v>-2.138379238795458</v>
       </c>
       <c r="G98">
-        <v>-6.512238181333932</v>
+        <v>-7.130439523700816</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.600998651249374</v>
       </c>
       <c r="E99">
-        <v>-43.09467702534763</v>
+        <v>-42.07139586773039</v>
       </c>
       <c r="F99">
-        <v>-1.979167852344796</v>
+        <v>-2.322541879785844</v>
       </c>
       <c r="G99">
-        <v>-6.826240115188265</v>
+        <v>-7.289143766307937</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.385750699966796</v>
       </c>
       <c r="E100">
-        <v>-44.10838046043865</v>
+        <v>-45.33869665697556</v>
       </c>
       <c r="F100">
-        <v>-2.062780772881169</v>
+        <v>-2.617574870701722</v>
       </c>
       <c r="G100">
-        <v>-6.318465329829311</v>
+        <v>-7.124636137370473</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.205663978126351</v>
       </c>
       <c r="E101">
-        <v>-47.0866785669883</v>
+        <v>-46.28882258123589</v>
       </c>
       <c r="F101">
-        <v>-2.035274833271212</v>
+        <v>-2.529254338215238</v>
       </c>
       <c r="G101">
-        <v>-6.309119659771948</v>
+        <v>-7.938090145098032</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.053420603077776</v>
       </c>
       <c r="E102">
-        <v>-49.7257611389269</v>
+        <v>-48.79985122942259</v>
       </c>
       <c r="F102">
-        <v>-2.39671638213472</v>
+        <v>-2.932936826049702</v>
       </c>
       <c r="G102">
-        <v>-6.227766313689898</v>
+        <v>-7.183113613776159</v>
       </c>
     </row>
   </sheetData>
